--- a/sample/注文書.xlsx
+++ b/sample/注文書.xlsx
@@ -10,46 +10,6 @@
 </workbook>
 </file>
 
-<file path=xl/joPython.xml><?xml version="1.0" encoding="utf-8"?>
-<joPython>
-  <script name="更新"># 品番マスタの写し(H〜J 列)をサーバーの正本と入れ替える。
-# 実行は「@更新 net」(網あり檻 — 許可はその場の操作だけ)。
-URL = "http://127.0.0.1:8765/catalog.csv"
-import urllib.request, csv, io
-raw = urllib.request.urlopen(URL, timeout=5).read()
-rows = list(csv.reader(io.StringIO(raw.decode("utf-8"))))[1:]
-for i, r in enumerate(rows):
-    n = 2 + i
-    s[f"H{n}"] = r[0]          # 品番
-    s[f"I{n}"] = r[2]          # 品名
-    s[f"J{n}"] = int(r[4])     # 単価
-for n in range(2 + len(rows), 41):   # 減った分の残骸は消す
-    s[f"H{n}"] = None; s[f"I{n}"] = None; s[f"J{n}"] = None
-b.recalc()
-print(f"品番マスタを {len(rows)} 品目に更新しました")
-</script>
-  <script name="送信"># 注文行(品番と数量の入った行)をサーバーへ送る。
-# 実行は「@送信 net」(網あり檻 — 許可はその場の操作だけ)。
-URL = "http://127.0.0.1:8765/order"
-import urllib.request, json
-lines = []
-for n in range(7, 17):
-    code, qty = s[f"A{n}"], s[f"D{n}"]
-    if code and qty:
-        lines.append({"品番": code, "数量": int(qty)})
-if not lines:
-    print("注文行がありません(品番と数量を入れてから)")
-else:
-    order = {"社名": s["B3"] or "(未記入)", "担当": s["D3"] or "", "明細": lines}
-    req = urllib.request.Request(
-        URL, json.dumps(order, ensure_ascii=False).encode("utf-8"),
-        {"Content-Type": "application/json"})
-    r = json.loads(urllib.request.urlopen(req, timeout=5).read().decode("utf-8"))
-    print(f"送信しました(受付番号 {r['受付番号']}・明細 {len(lines)} 行)")
-</script>
-</joPython>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
   <si>
@@ -224,7 +184,7 @@
     <t xml:space="preserve">パイプ式ファイルA4</t>
   </si>
   <si>
-    <t xml:space="preserve">データ &gt; Python: @更新 net でマスタを取り直し、@送信 net で注文を送る。</t>
+    <t xml:space="preserve">データ &gt; Python: @更新 net でマスタを取り直し、@送信 net で注文を送る(手続きは隣の 更新.py・送信.py を plugins へ)。</t>
   </si>
   <si>
     <t xml:space="preserve">C-303</t>
